--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4209,7 +4209,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>157</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>
@@ -4514,7 +4514,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>165</v>
       </c>
@@ -4529,13 +4529,13 @@
         <v>62</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>74</v>
@@ -4617,7 +4617,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>169</v>
       </c>
@@ -4632,13 +4632,13 @@
         <v>170</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4926,7 +4926,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>183</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$141</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4366" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4398" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -941,6 +941,22 @@
   </si>
   <si>
     <t>Material.lotNumberText</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturedMaterial.sdtcExpirationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>The date and time the manufacturer no longer ensures the safety, quality, and/or proper functioning of the material.</t>
+  </si>
+  <si>
+    <t>There is a need in many situations that the materials used are of a specific quality or potency or functional status. The ending date for this guarantee is specified by the manufacturer. After that date, while the material may still provide the same characteristics, the manufacturer no longer takes responsibility that the product will perform as specified and denies responsibility for failure of the material after that date.</t>
+  </si>
+  <si>
+    <t>Material.sdtcExpirationTime</t>
   </si>
   <si>
     <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturerOrganization</t>
@@ -1607,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK140"/>
+  <dimension ref="A1:AK141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.61328125" customWidth="true" bestFit="true"/>
@@ -1624,7 +1640,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -10783,9 +10799,13 @@
         <v>301</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
+      <c r="M91" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>74</v>
       </c>
@@ -10833,7 +10853,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10853,10 +10873,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10879,7 +10899,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10932,7 +10952,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10952,10 +10972,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10966,7 +10986,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>74</v>
@@ -10978,7 +10998,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11031,13 +11051,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>74</v>
@@ -11051,10 +11071,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11077,7 +11097,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11130,7 +11150,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11150,10 +11170,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11164,7 +11184,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -11176,14 +11196,10 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11233,7 +11249,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11253,10 +11269,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11267,7 +11283,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>74</v>
@@ -11279,10 +11295,14 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11332,7 +11352,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11352,10 +11372,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11378,7 +11398,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11431,7 +11451,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11449,12 +11469,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11465,10 +11485,10 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>74</v>
@@ -11477,14 +11497,10 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11534,7 +11550,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11552,20 +11568,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E99" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
@@ -11573,7 +11587,7 @@
         <v>75</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>74</v>
@@ -11582,11 +11596,13 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L99" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="M99" t="s" s="2">
-        <v>86</v>
+        <v>323</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11613,11 +11629,13 @@
         <v>74</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11635,13 +11653,13 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>89</v>
+        <v>321</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
@@ -11655,21 +11673,23 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>74</v>
@@ -11681,11 +11701,11 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11712,13 +11732,11 @@
         <v>74</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>74</v>
@@ -11736,13 +11754,13 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>74</v>
@@ -11756,10 +11774,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11770,7 +11788,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>74</v>
@@ -11782,11 +11800,11 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11837,19 +11855,19 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>74</v>
@@ -11857,18 +11875,16 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E102" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
@@ -11885,11 +11901,11 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11916,11 +11932,13 @@
         <v>74</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>74</v>
@@ -11938,7 +11956,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11950,7 +11968,7 @@
         <v>74</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>74</v>
@@ -11958,17 +11976,17 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>80</v>
@@ -11986,11 +12004,11 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12017,13 +12035,11 @@
         <v>74</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -12041,7 +12057,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12061,17 +12077,17 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>80</v>
@@ -12089,11 +12105,11 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12144,7 +12160,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12164,20 +12180,20 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>75</v>
@@ -12192,11 +12208,11 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12205,7 +12221,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>74</v>
@@ -12247,7 +12263,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12267,17 +12283,17 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>75</v>
@@ -12295,11 +12311,11 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12308,7 +12324,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>74</v>
@@ -12350,7 +12366,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12370,21 +12386,23 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F107" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>74</v>
@@ -12396,11 +12414,11 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12451,13 +12469,13 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>74</v>
@@ -12471,10 +12489,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12482,10 +12500,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>74</v>
@@ -12497,10 +12515,12 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
+      <c r="M108" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12511,7 +12531,7 @@
         <v>74</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>329</v>
+        <v>74</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>74</v>
@@ -12526,11 +12546,13 @@
         <v>74</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>330</v>
+        <v>74</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -12548,13 +12570,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>331</v>
+        <v>125</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12568,10 +12590,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12579,7 +12601,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>75</v>
@@ -12594,12 +12616,10 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" t="s" s="2">
-        <v>333</v>
-      </c>
+      <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -12610,7 +12630,7 @@
         <v>74</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>74</v>
@@ -12625,13 +12645,11 @@
         <v>74</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>74</v>
+        <v>335</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -12649,10 +12667,10 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>75</v>
@@ -12669,10 +12687,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12699,12 +12717,12 @@
       </c>
       <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
-        <v>337</v>
+        <v>74</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
@@ -12750,7 +12768,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12770,10 +12788,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12799,11 +12817,13 @@
         <v>107</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
+      <c r="M111" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
-        <v>74</v>
+        <v>342</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
@@ -12849,7 +12869,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12869,10 +12889,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12895,7 +12915,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>342</v>
+        <v>107</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12948,7 +12968,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12968,10 +12988,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12994,7 +13014,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13047,7 +13067,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13067,10 +13087,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13093,7 +13113,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13146,7 +13166,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13166,10 +13186,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13192,7 +13212,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13245,7 +13265,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13265,10 +13285,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13291,7 +13311,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13344,7 +13364,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13364,10 +13384,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13390,7 +13410,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13443,7 +13463,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13463,10 +13483,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13489,7 +13509,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13542,7 +13562,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13562,10 +13582,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13588,7 +13608,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13641,7 +13661,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13661,10 +13681,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13687,7 +13707,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13740,7 +13760,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13760,10 +13780,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13786,7 +13806,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -13839,7 +13859,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13859,10 +13879,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13885,7 +13905,7 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -13938,7 +13958,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -13956,12 +13976,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13975,7 +13995,7 @@
         <v>75</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>74</v>
@@ -13984,14 +14004,10 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14041,13 +14057,13 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>74</v>
@@ -14059,20 +14075,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E124" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
@@ -14080,7 +14094,7 @@
         <v>75</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>74</v>
@@ -14089,11 +14103,13 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L124" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="M124" t="s" s="2">
-        <v>86</v>
+        <v>381</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14120,11 +14136,13 @@
         <v>74</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y124" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z124" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>74</v>
@@ -14142,13 +14160,13 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>89</v>
+        <v>379</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>74</v>
@@ -14162,21 +14180,23 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E125" s="2"/>
+      <c r="E125" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>74</v>
@@ -14188,11 +14208,11 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14219,13 +14239,11 @@
         <v>74</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>74</v>
@@ -14243,13 +14261,13 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>74</v>
@@ -14263,10 +14281,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14277,7 +14295,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>74</v>
@@ -14289,11 +14307,11 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14344,19 +14362,19 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>74</v>
@@ -14364,18 +14382,16 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E127" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>80</v>
       </c>
@@ -14392,11 +14408,11 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14423,11 +14439,13 @@
         <v>74</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y127" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z127" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>74</v>
@@ -14445,7 +14463,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14457,7 +14475,7 @@
         <v>74</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>74</v>
@@ -14465,17 +14483,17 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F128" t="s" s="2">
         <v>80</v>
@@ -14493,11 +14511,11 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14524,13 +14542,11 @@
         <v>74</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>74</v>
@@ -14548,7 +14564,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14568,17 +14584,17 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F129" t="s" s="2">
         <v>80</v>
@@ -14596,11 +14612,11 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14651,7 +14667,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14671,20 +14687,20 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F130" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>75</v>
@@ -14699,11 +14715,11 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14712,7 +14728,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>74</v>
@@ -14754,7 +14770,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14774,17 +14790,17 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>75</v>
@@ -14802,11 +14818,11 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -14815,7 +14831,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>74</v>
@@ -14857,7 +14873,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14877,21 +14893,23 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E132" s="2"/>
+      <c r="E132" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F132" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>74</v>
@@ -14903,11 +14921,11 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -14958,13 +14976,13 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>74</v>
@@ -14978,10 +14996,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -14989,10 +15007,10 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>74</v>
@@ -15004,10 +15022,12 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L133" s="2"/>
-      <c r="M133" s="2"/>
+      <c r="M133" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -15018,7 +15038,7 @@
         <v>74</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>387</v>
+        <v>74</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>74</v>
@@ -15033,11 +15053,13 @@
         <v>74</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y133" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z133" t="s" s="2">
-        <v>388</v>
+        <v>74</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>74</v>
@@ -15055,13 +15077,13 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>389</v>
+        <v>125</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>74</v>
@@ -15075,10 +15097,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15086,7 +15108,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>75</v>
@@ -15101,7 +15123,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>345</v>
+        <v>85</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15115,7 +15137,7 @@
         <v>74</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>74</v>
+        <v>392</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>74</v>
@@ -15130,13 +15152,11 @@
         <v>74</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>74</v>
+        <v>393</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>74</v>
@@ -15154,10 +15174,10 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>75</v>
@@ -15174,10 +15194,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15200,7 +15220,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15253,7 +15273,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15273,10 +15293,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15299,7 +15319,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15352,7 +15372,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15372,10 +15392,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15398,7 +15418,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15451,7 +15471,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15469,12 +15489,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15482,13 +15502,13 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>74</v>
@@ -15497,7 +15517,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15550,7 +15570,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15568,12 +15588,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15581,13 +15601,13 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>74</v>
@@ -15596,7 +15616,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15649,13 +15669,13 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>74</v>
@@ -15669,10 +15689,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15695,7 +15715,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -15748,7 +15768,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -15766,8 +15786,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L141" s="2"/>
+      <c r="M141" s="2"/>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK140">
+  <autoFilter ref="A1:AK141">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15777,7 +15896,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI139">
+  <conditionalFormatting sqref="A2:AI140">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
